--- a/dataset/02.wo_Defects/double_release.xlsx
+++ b/dataset/02.wo_Defects/double_release.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pthread_mutex_t double_release_001_glb_mutex_; pthread_mutex_t * double_release_001_glb_mutex = &amp; double_release_001_glb_mutex_; int double_release_001_glb_data = 0; pthread_mutex_t double_release_002_glb_mutex_; pthread_mutex_t * double_release_002_glb_mutex = &amp;double_release_002_glb_mutex_; int double_release_002_glb_data = 0; pthread_mutex_t double_release_003_glb_mutex_; pthread_mutex_t * double_release_003_glb_mutex = &amp; double_release_003_glb_mutex_; int double_release_003_glb_data = 0; pthread_mutex_t double_release_004_glb_mutex_; pthread_mutex_t * double_release_004_glb_mutex = &amp; double_release_004_glb_mutex_; int double_release_004_glb_data = 0; pthread_mutex_t double_release_005_glb_mutex_; pthread_mutex_t * double_release_005_glb_mutex = &amp; double_release_005_glb_mutex_; int double_release_005_glb_data = 0; pthread_mutex_t double_release_006_glb_mutex_; pthread_mutex_t * double_release_006_glb_mutex = &amp; double_release_006_glb_mutex_; int double_release_006_glb_data = 0; extern volatile int vflag; void double_release_002 () { pthread_t tid1,tid2; pthread_mutex_init (double_release_002_glb_mutex, NULL); pthread_create (&amp; tid1, NULL, double_release_002_tsk_001, NULL); pthread_create (&amp; tid2, NULL, double_release_002_tsk_002, NULL); pthread_join (tid1, NULL); pthread_join (tid2, NULL); pthread_mutex_destroy (double_release_002_glb_mutex); } void * double_release_002_tsk_002 (void * pram) { pthread_mutex_lock (double_release_002_glb_mutex); double_release_002_glb_data = (double_release_002_glb_data% 100) + 1; pthread_mutex_unlock (double_release_002_glb_mutex); return NULL; } void * double_release_002_tsk_001 (void * pram) { pthread_mutex_lock (double_release_002_glb_mutex); double_release_002_glb_data = (double_release_002_glb_data% 100) + 1; pthread_mutex_unlock (double_release_002_glb_mutex); return NULL; }</t>
+          <t>pthread_mutex_t double_release_001_glb_mutex_; pthread_mutex_t * double_release_001_glb_mutex = &amp; double_release_001_glb_mutex_; int double_release_001_glb_data = 0; pthread_mutex_t double_release_002_glb_mutex_; pthread_mutex_t * double_release_002_glb_mutex = &amp;double_release_002_glb_mutex_; int double_release_002_glb_data = 0; pthread_mutex_t double_release_003_glb_mutex_; pthread_mutex_t * double_release_003_glb_mutex = &amp; double_release_003_glb_mutex_; int double_release_003_glb_data = 0; pthread_mutex_t double_release_004_glb_mutex_; pthread_mutex_t * double_release_004_glb_mutex = &amp; double_release_004_glb_mutex_; int double_release_004_glb_data = 0; pthread_mutex_t double_release_005_glb_mutex_; pthread_mutex_t * double_release_005_glb_mutex = &amp; double_release_005_glb_mutex_; int double_release_005_glb_data = 0; pthread_mutex_t double_release_006_glb_mutex_; pthread_mutex_t * double_release_006_glb_mutex = &amp; double_release_006_glb_mutex_; int double_release_006_glb_data = 0; extern volatile int vflag; void double_release_002 () { pthread_t tid1,tid2; pthread_mutex_init (double_release_002_glb_mutex, NULL); pthread_create (&amp; tid1, NULL, double_release_002_tsk_001, NULL); pthread_create (&amp; tid2, NULL, double_release_002_tsk_002, NULL); pthread_join (tid1, NULL); pthread_join (tid2, NULL); pthread_mutex_destroy (double_release_002_glb_mutex); } void * double_release_002_tsk_001 (void * pram) { pthread_mutex_lock (double_release_002_glb_mutex); double_release_002_glb_data = (double_release_002_glb_data% 100) + 1; pthread_mutex_unlock (double_release_002_glb_mutex); return NULL; } void * double_release_002_tsk_002 (void * pram) { pthread_mutex_lock (double_release_002_glb_mutex); double_release_002_glb_data = (double_release_002_glb_data% 100) + 1; pthread_mutex_unlock (double_release_002_glb_mutex); return NULL; }</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
